--- a/y11518/exports/工单导出_2026-05-25.xlsx
+++ b/y11518/exports/工单导出_2026-05-25.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -484,34 +484,34 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>WO202605250002</v>
+        <v>WO202605250003</v>
       </c>
       <c r="B3" t="str">
-        <v>站点B区</v>
+        <v>站点C区</v>
       </c>
       <c r="C3" t="str">
-        <v>用户2</v>
+        <v>用户3</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-23 15:30:49</v>
+        <v>2026-05-22 01:15:49</v>
       </c>
       <c r="E3" t="str">
         <v>已完成</v>
       </c>
       <c r="F3" t="str">
-        <v>夜间抢修1队</v>
+        <v>抢修队</v>
       </c>
       <c r="G3" t="str">
-        <v>李夜</v>
+        <v>张队</v>
       </c>
       <c r="H3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="I3">
-        <v>2640</v>
+        <v>5530</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3" t="str">
         <v>否</v>
@@ -523,139 +523,16 @@
         <v>2026-05-25 13:20:49</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>WO202605250003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>站点C区</v>
-      </c>
-      <c r="C4" t="str">
-        <v>用户3</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-22 01:15:49</v>
-      </c>
-      <c r="E4" t="str">
-        <v>已完成</v>
-      </c>
-      <c r="F4" t="str">
-        <v>抢修队</v>
-      </c>
-      <c r="G4" t="str">
-        <v>张队</v>
-      </c>
-      <c r="H4">
-        <v>500</v>
-      </c>
-      <c r="I4">
-        <v>5530</v>
-      </c>
-      <c r="J4">
-        <v>4</v>
-      </c>
-      <c r="K4" t="str">
-        <v>否</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v>2026-05-25 13:20:49</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>WO202605250004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>站点D区</v>
-      </c>
-      <c r="C5" t="str">
-        <v>用户4</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-21 01:15:49</v>
-      </c>
-      <c r="E5" t="str">
-        <v>已完成</v>
-      </c>
-      <c r="F5" t="str">
-        <v>抢修队</v>
-      </c>
-      <c r="G5" t="str">
-        <v>张队</v>
-      </c>
-      <c r="H5">
-        <v>500</v>
-      </c>
-      <c r="I5">
-        <v>5870</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5" t="str">
-        <v>否</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v>2026-05-25 13:20:49</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>WO202605250005</v>
-      </c>
-      <c r="B6" t="str">
-        <v>站点E区</v>
-      </c>
-      <c r="C6" t="str">
-        <v>用户5</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-20 01:15:49</v>
-      </c>
-      <c r="E6" t="str">
-        <v>已完成</v>
-      </c>
-      <c r="F6" t="str">
-        <v>抢修队</v>
-      </c>
-      <c r="G6" t="str">
-        <v>张队</v>
-      </c>
-      <c r="H6">
-        <v>500</v>
-      </c>
-      <c r="I6">
-        <v>1460</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6" t="str">
-        <v>否</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
-        <v>2026-05-25 13:20:49</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -804,7 +681,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>WO202605250002</v>
+        <v>WO202605250003</v>
       </c>
       <c r="B6" t="str">
         <v>VLV-001</v>
@@ -833,7 +710,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>WO202605250002</v>
+        <v>WO202605250003</v>
       </c>
       <c r="B7" t="str">
         <v>VLV-002</v>
@@ -865,25 +742,25 @@
         <v>WO202605250003</v>
       </c>
       <c r="B8" t="str">
-        <v>VLV-001</v>
+        <v>VLV-003</v>
       </c>
       <c r="C8" t="str">
-        <v>DN50闸阀</v>
+        <v>DN100闸阀</v>
       </c>
       <c r="D8" t="str">
-        <v>DN50,1.6MPa</v>
+        <v>DN100,1.6MPa</v>
       </c>
       <c r="E8" t="str">
         <v>个</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>280</v>
+        <v>680</v>
       </c>
       <c r="H8">
-        <v>840</v>
+        <v>2720</v>
       </c>
       <c r="I8" t="str">
         <v>否</v>
@@ -894,236 +771,33 @@
         <v>WO202605250003</v>
       </c>
       <c r="B9" t="str">
-        <v>VLV-002</v>
+        <v>PIPE-001</v>
       </c>
       <c r="C9" t="str">
-        <v>DN80闸阀</v>
+        <v>PE管DN50</v>
       </c>
       <c r="D9" t="str">
-        <v>DN80,1.6MPa</v>
+        <v>DN50,1.0MPa</v>
       </c>
       <c r="E9" t="str">
-        <v>个</v>
+        <v>米</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>450</v>
+        <v>85</v>
       </c>
       <c r="H9">
-        <v>1800</v>
+        <v>170</v>
       </c>
       <c r="I9" t="str">
-        <v>否</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>WO202605250003</v>
-      </c>
-      <c r="B10" t="str">
-        <v>VLV-003</v>
-      </c>
-      <c r="C10" t="str">
-        <v>DN100闸阀</v>
-      </c>
-      <c r="D10" t="str">
-        <v>DN100,1.6MPa</v>
-      </c>
-      <c r="E10" t="str">
-        <v>个</v>
-      </c>
-      <c r="F10">
-        <v>4</v>
-      </c>
-      <c r="G10">
-        <v>680</v>
-      </c>
-      <c r="H10">
-        <v>2720</v>
-      </c>
-      <c r="I10" t="str">
-        <v>否</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>WO202605250003</v>
-      </c>
-      <c r="B11" t="str">
-        <v>PIPE-001</v>
-      </c>
-      <c r="C11" t="str">
-        <v>PE管DN50</v>
-      </c>
-      <c r="D11" t="str">
-        <v>DN50,1.0MPa</v>
-      </c>
-      <c r="E11" t="str">
-        <v>米</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11">
-        <v>85</v>
-      </c>
-      <c r="H11">
-        <v>170</v>
-      </c>
-      <c r="I11" t="str">
-        <v>否</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>WO202605250004</v>
-      </c>
-      <c r="B12" t="str">
-        <v>VLV-001</v>
-      </c>
-      <c r="C12" t="str">
-        <v>DN50闸阀</v>
-      </c>
-      <c r="D12" t="str">
-        <v>DN50,1.6MPa</v>
-      </c>
-      <c r="E12" t="str">
-        <v>个</v>
-      </c>
-      <c r="F12">
-        <v>4</v>
-      </c>
-      <c r="G12">
-        <v>280</v>
-      </c>
-      <c r="H12">
-        <v>1120</v>
-      </c>
-      <c r="I12" t="str">
-        <v>否</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>WO202605250004</v>
-      </c>
-      <c r="B13" t="str">
-        <v>VLV-002</v>
-      </c>
-      <c r="C13" t="str">
-        <v>DN80闸阀</v>
-      </c>
-      <c r="D13" t="str">
-        <v>DN80,1.6MPa</v>
-      </c>
-      <c r="E13" t="str">
-        <v>个</v>
-      </c>
-      <c r="F13">
-        <v>3</v>
-      </c>
-      <c r="G13">
-        <v>450</v>
-      </c>
-      <c r="H13">
-        <v>1350</v>
-      </c>
-      <c r="I13" t="str">
-        <v>否</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>WO202605250004</v>
-      </c>
-      <c r="B14" t="str">
-        <v>VLV-003</v>
-      </c>
-      <c r="C14" t="str">
-        <v>DN100闸阀</v>
-      </c>
-      <c r="D14" t="str">
-        <v>DN100,1.6MPa</v>
-      </c>
-      <c r="E14" t="str">
-        <v>个</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-      <c r="G14">
-        <v>680</v>
-      </c>
-      <c r="H14">
-        <v>3400</v>
-      </c>
-      <c r="I14" t="str">
-        <v>否</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>WO202605250005</v>
-      </c>
-      <c r="B15" t="str">
-        <v>VLV-001</v>
-      </c>
-      <c r="C15" t="str">
-        <v>DN50闸阀</v>
-      </c>
-      <c r="D15" t="str">
-        <v>DN50,1.6MPa</v>
-      </c>
-      <c r="E15" t="str">
-        <v>个</v>
-      </c>
-      <c r="F15">
-        <v>2</v>
-      </c>
-      <c r="G15">
-        <v>280</v>
-      </c>
-      <c r="H15">
-        <v>560</v>
-      </c>
-      <c r="I15" t="str">
-        <v>否</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>WO202605250005</v>
-      </c>
-      <c r="B16" t="str">
-        <v>VLV-002</v>
-      </c>
-      <c r="C16" t="str">
-        <v>DN80闸阀</v>
-      </c>
-      <c r="D16" t="str">
-        <v>DN80,1.6MPa</v>
-      </c>
-      <c r="E16" t="str">
-        <v>个</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-      <c r="G16">
-        <v>450</v>
-      </c>
-      <c r="H16">
-        <v>900</v>
-      </c>
-      <c r="I16" t="str">
         <v>否</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
   </ignoredErrors>
 </worksheet>
 </file>